--- a/source/人工智能场景计划表-0810.xlsx
+++ b/source/人工智能场景计划表-0810.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="207">
   <si>
     <t>浙江电力交易中心人工智能场景建设计划表</t>
   </si>
@@ -197,42 +197,36 @@
     <t>绿色消费核算数据稽核</t>
   </si>
   <si>
-    <t>绿电零售与绿电批发消费核算</t>
+    <t>基础数据稽核</t>
   </si>
   <si>
     <t>张晓龙</t>
   </si>
   <si>
-    <t>已有前端效果展示</t>
-  </si>
-  <si>
-    <t>自发自用消费核算</t>
-  </si>
-  <si>
-    <t>用网电量营销零售对比稽核</t>
+    <t>绿电消费核算溯源分析</t>
+  </si>
+  <si>
+    <t>部分完成</t>
+  </si>
+  <si>
+    <t>绿电批发与绿电零售已有前端效果</t>
   </si>
   <si>
     <t>新一代人工智能试点，非化石能源建设</t>
   </si>
   <si>
-    <t>基础数据校验</t>
-  </si>
-  <si>
-    <t>负责人黄恒孜，对接人张晓龙</t>
-  </si>
-  <si>
-    <t>指标智能生成</t>
-  </si>
-  <si>
-    <t>非化石核算结果校验与溯源</t>
+    <t>指标智能生成（内+外）</t>
+  </si>
+  <si>
+    <t>非化石报表数据稽核</t>
+  </si>
+  <si>
+    <t>非化石计算过程skill</t>
   </si>
   <si>
     <t>非化石指标分摊方案设计</t>
   </si>
   <si>
-    <t>非化石计算过程skill</t>
-  </si>
-  <si>
     <t>结算信息披露智能问数</t>
   </si>
   <si>
@@ -257,6 +251,12 @@
     <t>事后报表数据稽核</t>
   </si>
   <si>
+    <t>大屏人工智能讲解</t>
+  </si>
+  <si>
+    <t>人工智能自动项目跟进</t>
+  </si>
+  <si>
     <t>合规部</t>
   </si>
   <si>
@@ -321,9 +321,6 @@
   </si>
   <si>
     <t>自动回归测试</t>
-  </si>
-  <si>
-    <t>部分完成</t>
   </si>
   <si>
     <t>12月31日</t>
@@ -599,15 +596,24 @@
     <t>交易部</t>
   </si>
   <si>
+    <t>交易快报智能生成</t>
+  </si>
+  <si>
+    <t>指标数据自动汇聚</t>
+  </si>
+  <si>
+    <t>骆希</t>
+  </si>
+  <si>
+    <t>交易快报一键生成</t>
+  </si>
+  <si>
     <t>交易全流程自动化</t>
   </si>
   <si>
     <t>交易序列创建</t>
   </si>
   <si>
-    <t>骆希</t>
-  </si>
-  <si>
     <t>设置限额</t>
   </si>
   <si>
@@ -617,16 +623,19 @@
     <t>信息披露发布</t>
   </si>
   <si>
+    <t>一键触发交易</t>
+  </si>
+  <si>
+    <t>全省市场化响应自助交易</t>
+  </si>
+  <si>
+    <t>交易出清智能校核</t>
+  </si>
+  <si>
     <t>事前辅助出清各元素的智能校核</t>
   </si>
   <si>
     <t>事后出清结果的智能复核</t>
-  </si>
-  <si>
-    <t>一键触发交易</t>
-  </si>
-  <si>
-    <t>全省市场化响应自助交易</t>
   </si>
   <si>
     <r>
@@ -653,6 +662,9 @@
       </rPr>
       <t>全国统一电力市场</t>
     </r>
+  </si>
+  <si>
+    <t>需求发起方是北交，承接北交的任务，具体需求待定</t>
   </si>
   <si>
     <t>客服中心</t>
@@ -806,16 +818,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <charset val="134"/>
@@ -824,6 +826,16 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="DengXian"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1184,7 +1196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1242,6 +1254,113 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1368,7 +1487,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1380,34 +1499,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1493,7 +1612,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1562,49 +1681,127 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1680,10 +1877,10 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0" dbFileVersion="0" changeLogVersion="0">
-    <open main="47" threadCnt="1"/>
+    <open main="49" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="1">
-        <open main="2" threadCnt="1"/>
+        <open main="3" threadCnt="1"/>
       </sheetInfo>
     </sheetInfos>
   </bookInfo>
@@ -1885,7 +2082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -2156,7 +2353,7 @@
       <c r="J7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="15" t="s">
@@ -2196,7 +2393,7 @@
       <c r="J8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="15" t="s">
@@ -2236,7 +2433,7 @@
       <c r="J9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="15" t="s">
@@ -2276,7 +2473,7 @@
       <c r="J10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="15" t="s">
@@ -2484,29 +2681,27 @@
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="12">
-        <v>6</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46234</v>
+      <c r="E16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G16" s="13">
-        <v>46295</v>
+        <v>46386</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>24</v>
@@ -2520,26 +2715,18 @@
       <c r="L16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" ht="28.5" spans="1:14">
+      <c r="A17" s="12"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="12">
-        <v>6</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="25" t="s">
         <v>59</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="13">
         <v>46234</v>
@@ -2562,32 +2749,28 @@
       <c r="L17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="12" t="s">
-        <v>58</v>
+      <c r="M17" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="12">
-        <v>6</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>60</v>
+      <c r="A18" s="12"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="13">
-        <v>46234</v>
+      <c r="F18" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G18" s="13">
-        <v>46295</v>
+        <v>46386</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>24</v>
@@ -2604,19 +2787,15 @@
       <c r="L18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="12" t="s">
-        <v>58</v>
-      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="12"/>
     </row>
-    <row r="19" ht="28.5" spans="1:14">
+    <row r="19" spans="1:14">
       <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>62</v>
+      <c r="B19" s="26"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>24</v>
@@ -2631,7 +2810,7 @@
         <v>24</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>26</v>
@@ -2643,14 +2822,12 @@
         <v>22</v>
       </c>
       <c r="M19" s="12"/>
-      <c r="N19" s="12" t="s">
-        <v>63</v>
-      </c>
+      <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="24"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="12" t="s">
         <v>64</v>
       </c>
@@ -2667,7 +2844,7 @@
         <v>24</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>26</v>
@@ -2683,8 +2860,8 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="24"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="12" t="s">
         <v>65</v>
       </c>
@@ -2716,11 +2893,15 @@
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="24"/>
+      <c r="A22" s="12">
+        <v>7</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="18" t="s">
+        <v>66</v>
+      </c>
       <c r="D22" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>24</v>
@@ -2729,19 +2910,19 @@
         <v>25</v>
       </c>
       <c r="G22" s="13">
-        <v>46386</v>
+        <v>46326</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L22" s="14" t="s">
         <v>22</v>
@@ -2750,11 +2931,15 @@
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="12">
+        <v>7</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="D23" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>24</v>
@@ -2763,7 +2948,7 @@
         <v>25</v>
       </c>
       <c r="G23" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>24</v>
@@ -2775,7 +2960,7 @@
         <v>26</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L23" s="14" t="s">
         <v>22</v>
@@ -2784,17 +2969,13 @@
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="12">
-        <v>7</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>68</v>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26" t="s">
+        <v>70</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>24</v>
@@ -2803,7 +2984,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="13">
-        <v>46326</v>
+        <v>46386</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>24</v>
@@ -2812,10 +2993,10 @@
         <v>19</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L24" s="14" t="s">
         <v>22</v>
@@ -2824,29 +3005,23 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="12">
-        <v>7</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>68</v>
-      </c>
+      <c r="A25" s="22"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>25</v>
+        <v>73</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="13">
+        <v>46233</v>
       </c>
       <c r="G25" s="13">
-        <v>46265</v>
+        <v>46386</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>19</v>
@@ -2855,7 +3030,7 @@
         <v>26</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L25" s="14" t="s">
         <v>22</v>
@@ -2864,13 +3039,11 @@
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="26"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>73</v>
+      <c r="A26" s="22"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -2888,10 +3061,10 @@
         <v>19</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="L26" s="14" t="s">
         <v>22</v>
@@ -2901,24 +3074,22 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="22"/>
-      <c r="B27" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="B27" s="22"/>
       <c r="C27" s="22"/>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="13">
-        <v>46233</v>
+      <c r="E27" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G27" s="13">
         <v>46386</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>19</v>
@@ -2927,7 +3098,7 @@
         <v>26</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="L27" s="14" t="s">
         <v>22</v>
@@ -3057,7 +3228,7 @@
       <c r="M30" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="N30" s="27"/>
+      <c r="N30" s="30"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="12">
@@ -3227,17 +3398,17 @@
         <v>90</v>
       </c>
       <c r="C35" s="26"/>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="31" t="s">
         <v>97</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>24</v>
@@ -3254,10 +3425,10 @@
       <c r="L35" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M35" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="N35" s="29"/>
+      <c r="M35" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="N35" s="32"/>
     </row>
     <row r="36" ht="71.25" spans="1:14">
       <c r="A36" s="12">
@@ -3267,17 +3438,17 @@
         <v>90</v>
       </c>
       <c r="C36" s="26"/>
-      <c r="D36" s="28" t="s">
-        <v>101</v>
+      <c r="D36" s="31" t="s">
+        <v>100</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>24</v>
@@ -3294,11 +3465,11 @@
       <c r="L36" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M36" s="29" t="s">
+      <c r="M36" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="N36" s="33" t="s">
         <v>102</v>
-      </c>
-      <c r="N36" s="30" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:14">
@@ -3310,7 +3481,7 @@
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>24</v>
@@ -3319,7 +3490,7 @@
         <v>25</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>24</v>
@@ -3336,9 +3507,9 @@
       <c r="L37" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M37" s="31"/>
-      <c r="N37" s="29" t="s">
-        <v>105</v>
+      <c r="M37" s="34"/>
+      <c r="N37" s="32" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -3346,7 +3517,7 @@
       <c r="B38" s="12"/>
       <c r="C38" s="22"/>
       <c r="D38" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>24</v>
@@ -3355,7 +3526,7 @@
         <v>25</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>24</v>
@@ -3383,10 +3554,10 @@
         <v>90</v>
       </c>
       <c r="C39" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>18</v>
@@ -3407,14 +3578,14 @@
         <v>94</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L39" s="14" t="s">
         <v>96</v>
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -3425,10 +3596,10 @@
         <v>90</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>18</v>
@@ -3437,7 +3608,7 @@
         <v>93</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>19</v>
@@ -3449,7 +3620,7 @@
         <v>94</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L40" s="14" t="s">
         <v>96</v>
@@ -3465,13 +3636,13 @@
         <v>90</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="E41" s="12" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>93</v>
@@ -3495,8 +3666,8 @@
         <v>96</v>
       </c>
       <c r="M41" s="12"/>
-      <c r="N41" s="28" t="s">
-        <v>115</v>
+      <c r="N41" s="31" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="42" ht="33" spans="1:14">
@@ -3507,13 +3678,13 @@
         <v>90</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>59</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>93</v>
@@ -3531,16 +3702,16 @@
         <v>94</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L42" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M42" s="30" t="s">
+      <c r="M42" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="N42" s="33" t="s">
         <v>117</v>
-      </c>
-      <c r="N42" s="30" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:14">
@@ -3551,10 +3722,10 @@
         <v>90</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>118</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>18</v>
@@ -3575,12 +3746,12 @@
         <v>94</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L43" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="30"/>
+      <c r="M43" s="33"/>
       <c r="N43" s="12"/>
     </row>
     <row r="44" ht="42.75" spans="1:14">
@@ -3591,19 +3762,19 @@
         <v>90</v>
       </c>
       <c r="C44" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G44" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>123</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>19</v>
@@ -3621,10 +3792,10 @@
         <v>96</v>
       </c>
       <c r="M44" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="N44" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -3632,12 +3803,12 @@
       <c r="B45" s="12"/>
       <c r="C45" s="19"/>
       <c r="D45" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="32" t="s">
+      <c r="F45" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G45" s="13">
@@ -3666,12 +3837,12 @@
       <c r="B46" s="12"/>
       <c r="C46" s="19"/>
       <c r="D46" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="32" t="s">
+      <c r="F46" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G46" s="13">
@@ -3689,12 +3860,12 @@
       <c r="K46" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L46" s="33" t="s">
+      <c r="L46" s="36" t="s">
         <v>22</v>
       </c>
       <c r="M46" s="12"/>
       <c r="N46" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -3705,19 +3876,19 @@
         <v>90</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>24</v>
@@ -3743,10 +3914,10 @@
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>131</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>24</v>
@@ -3769,7 +3940,7 @@
       <c r="K48" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L48" s="33" t="s">
+      <c r="L48" s="36" t="s">
         <v>22</v>
       </c>
       <c r="M48" s="12"/>
@@ -3783,19 +3954,19 @@
         <v>90</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="31" t="s">
         <v>132</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>133</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>19</v>
@@ -3807,9 +3978,9 @@
         <v>20</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="L49" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="L49" s="36" t="s">
         <v>52</v>
       </c>
       <c r="M49" s="12"/>
@@ -3823,19 +3994,19 @@
         <v>90</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>136</v>
+        <v>131</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>135</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>19</v>
@@ -3847,9 +4018,9 @@
         <v>20</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="L50" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="L50" s="36" t="s">
         <v>52</v>
       </c>
       <c r="M50" s="12"/>
@@ -3860,12 +4031,12 @@
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="32" t="s">
+      <c r="F51" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G51" s="13">
@@ -3886,8 +4057,8 @@
       <c r="L51" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M51" s="29" t="s">
-        <v>138</v>
+      <c r="M51" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="N51" s="12"/>
     </row>
@@ -3895,13 +4066,13 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
-      <c r="D52" s="28" t="s">
-        <v>139</v>
+      <c r="D52" s="31" t="s">
+        <v>138</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="32" t="s">
+      <c r="F52" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G52" s="13">
@@ -3924,7 +4095,7 @@
       </c>
       <c r="M52" s="12"/>
       <c r="N52" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" ht="28.5" spans="1:14">
@@ -3935,19 +4106,19 @@
         <v>90</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>24</v>
       </c>
       <c r="F53" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G53" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>24</v>
@@ -3959,14 +4130,14 @@
         <v>94</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L53" s="14" t="s">
         <v>22</v>
       </c>
       <c r="M53" s="12"/>
       <c r="N53" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" ht="28.5" spans="1:14">
@@ -3977,10 +4148,10 @@
         <v>90</v>
       </c>
       <c r="C54" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>144</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>24</v>
@@ -4007,7 +4178,7 @@
         <v>96</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N54" s="12"/>
     </row>
@@ -4019,10 +4190,10 @@
         <v>90</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>24</v>
@@ -4059,10 +4230,10 @@
         <v>90</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -4098,11 +4269,11 @@
       <c r="B57" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>24</v>
@@ -4111,16 +4282,16 @@
         <v>25</v>
       </c>
       <c r="G57" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>151</v>
       </c>
       <c r="K57" s="12" t="s">
         <v>95</v>
@@ -4129,24 +4300,24 @@
         <v>96</v>
       </c>
       <c r="M57" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="N57" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="N57" s="12" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="12">
+      <c r="A58" s="20">
         <v>21</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C58" s="34" t="s">
-        <v>148</v>
+      <c r="C58" s="38" t="s">
+        <v>147</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>24</v>
@@ -4155,16 +4326,16 @@
         <v>25</v>
       </c>
       <c r="G58" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>151</v>
       </c>
       <c r="K58" s="12" t="s">
         <v>95</v>
@@ -4176,38 +4347,38 @@
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="12">
+      <c r="A59" s="39">
         <v>21</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="D59" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="F59" s="13">
-        <v>46234</v>
+      <c r="F59" s="35" t="s">
+        <v>25</v>
       </c>
       <c r="G59" s="13">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>20</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L59" s="14" t="s">
         <v>52</v>
@@ -4216,38 +4387,32 @@
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="12">
-        <v>22</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="13">
-        <v>46234</v>
+      <c r="A60" s="43"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>25</v>
       </c>
       <c r="G60" s="13">
-        <v>46265</v>
+        <v>46249</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J60" s="12" t="s">
         <v>20</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L60" s="14" t="s">
         <v>52</v>
@@ -4256,220 +4421,194 @@
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="12">
+      <c r="A61" s="39">
         <v>22</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="12" t="s">
+      <c r="B61" s="44"/>
+      <c r="C61" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="E61" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F61" s="13">
+      <c r="E61" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="48">
         <v>46234</v>
       </c>
-      <c r="G61" s="13">
-        <v>46265</v>
+      <c r="G61" s="48">
+        <v>46241</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L61" s="14" t="s">
+      <c r="K61" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="L61" s="49" t="s">
         <v>52</v>
       </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="12">
-        <v>22</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D62" s="12" t="s">
+      <c r="A62" s="50"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="13">
+      <c r="E62" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" s="48">
         <v>46234</v>
       </c>
-      <c r="G62" s="13">
+      <c r="G62" s="48">
         <v>46265</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L62" s="14" t="s">
+      <c r="K62" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="L62" s="49" t="s">
         <v>52</v>
       </c>
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="12">
-        <v>22</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D63" s="12" t="s">
+      <c r="A63" s="50"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="E63" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="13">
+      <c r="E63" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="48">
         <v>46234</v>
       </c>
-      <c r="G63" s="13">
-        <v>46386</v>
+      <c r="G63" s="48">
+        <v>46265</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I63" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L63" s="14" t="s">
+      <c r="K63" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="L63" s="49" t="s">
         <v>52</v>
       </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="12">
-        <v>22</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D64" s="12" t="s">
+      <c r="A64" s="50"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="51"/>
+      <c r="D64" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="13">
+      <c r="E64" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="48">
         <v>46234</v>
       </c>
-      <c r="G64" s="13">
-        <v>46386</v>
+      <c r="G64" s="48">
+        <v>46265</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" s="12" t="s">
+      <c r="I64" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K64" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L64" s="14" t="s">
+      <c r="K64" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="L64" s="49" t="s">
         <v>52</v>
       </c>
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="12" t="s">
+      <c r="A65" s="50"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" s="13" t="s">
+      <c r="E65" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G65" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I65" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" s="12" t="s">
+      <c r="I65" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K65" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L65" s="14" t="s">
+      <c r="K65" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="L65" s="49" t="s">
         <v>52</v>
       </c>
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="12">
-        <v>22</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D66" s="12" t="s">
+      <c r="A66" s="43"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="E66" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" s="13" t="s">
+      <c r="E66" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G66" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>24</v>
@@ -4481,7 +4620,7 @@
         <v>20</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L66" s="14" t="s">
         <v>52</v>
@@ -4489,79 +4628,71 @@
       <c r="M66" s="12"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" ht="16.95" customHeight="1" spans="1:14">
-      <c r="A67" s="12">
-        <v>22</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C67" s="35" t="s">
+    <row r="67" spans="1:14">
+      <c r="A67" s="39">
+        <v>23</v>
+      </c>
+      <c r="B67" s="44"/>
+      <c r="C67" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>25</v>
+      <c r="D67" s="52" t="s">
+        <v>167</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>25</v>
+      <c r="F67" s="13">
+        <v>46234</v>
+      </c>
+      <c r="G67" s="13">
+        <v>46386</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" ht="27" spans="1:14">
-      <c r="A68" s="12">
-        <v>23</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="36" t="s">
+    <row r="68" spans="1:14">
+      <c r="A68" s="43"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>18</v>
+      <c r="E68" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="F68" s="13">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="G68" s="13">
-        <v>46265</v>
+        <v>46386</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="L68" s="14" t="s">
         <v>52</v>
@@ -4569,57 +4700,61 @@
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14">
-      <c r="A69" s="12">
+    <row r="69" ht="16.95" customHeight="1" spans="1:14">
+      <c r="A69" s="55">
+        <v>24</v>
+      </c>
+      <c r="B69" s="56"/>
+      <c r="C69" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C69" s="37"/>
-      <c r="D69" s="14" t="s">
+      <c r="E69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69" s="12"/>
+      <c r="N69" s="25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" ht="27" spans="1:14">
+      <c r="A70" s="22">
+        <v>25</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="C70" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E70" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="F69" s="13">
-        <v>46241</v>
-      </c>
-      <c r="G69" s="13">
-        <v>46265</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K69" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="L69" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="12">
-        <v>25</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C70" s="38"/>
-      <c r="D70" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>24</v>
       </c>
       <c r="F70" s="13">
         <v>46241</v>
@@ -4628,16 +4763,16 @@
         <v>46265</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="14" t="s">
         <v>24</v>
       </c>
       <c r="J70" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L70" s="14" t="s">
         <v>52</v>
@@ -4647,28 +4782,26 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>25</v>
+        <v>171</v>
+      </c>
+      <c r="C71" s="59"/>
+      <c r="D71" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="13">
+        <v>46241</v>
       </c>
       <c r="G71" s="13">
-        <v>46325</v>
+        <v>46265</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>24</v>
@@ -4677,7 +4810,7 @@
         <v>26</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L71" s="14" t="s">
         <v>52</v>
@@ -4687,25 +4820,23 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>173</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C72" s="60"/>
       <c r="D72" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>25</v>
+        <v>176</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="13">
+        <v>46241</v>
       </c>
       <c r="G72" s="13">
-        <v>46325</v>
+        <v>46265</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>24</v>
@@ -4717,7 +4848,7 @@
         <v>26</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L72" s="14" t="s">
         <v>52</v>
@@ -4730,13 +4861,13 @@
         <v>26</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>24</v>
@@ -4757,7 +4888,7 @@
         <v>26</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L73" s="14" t="s">
         <v>52</v>
@@ -4770,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>24</v>
@@ -4797,7 +4928,7 @@
         <v>26</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L74" s="14" t="s">
         <v>52</v>
@@ -4807,16 +4938,16 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>178</v>
+        <v>171</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>24</v>
@@ -4825,19 +4956,19 @@
         <v>25</v>
       </c>
       <c r="G75" s="13">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J75" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L75" s="14" t="s">
         <v>52</v>
@@ -4847,14 +4978,16 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" s="24"/>
+        <v>171</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="D76" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>24</v>
@@ -4863,19 +4996,19 @@
         <v>25</v>
       </c>
       <c r="G76" s="13">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="H76" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J76" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L76" s="14" t="s">
         <v>52</v>
@@ -4884,15 +5017,17 @@
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="12">
+      <c r="A77" s="61">
         <v>27</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C77" s="24"/>
+        <v>171</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="D77" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>24</v>
@@ -4912,8 +5047,8 @@
       <c r="J77" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="14" t="s">
-        <v>170</v>
+      <c r="K77" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="L77" s="14" t="s">
         <v>52</v>
@@ -4922,32 +5057,34 @@
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="E78" s="14" t="s">
+      <c r="A78" s="62"/>
+      <c r="B78" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" s="29"/>
+      <c r="D78" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F78" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G78" s="13">
-        <v>46386</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I78" s="14" t="s">
+        <v>46295</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L78" s="14" t="s">
         <v>52</v>
@@ -4956,80 +5093,68 @@
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="12">
-        <v>27</v>
-      </c>
+      <c r="A79" s="62"/>
       <c r="B79" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>183</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C79" s="29"/>
       <c r="D79" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="13">
-        <v>46241</v>
+        <v>185</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G79" s="13">
-        <v>46249</v>
+        <v>46295</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I79" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J79" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="12" t="s">
-        <v>170</v>
+      <c r="J79" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>174</v>
       </c>
       <c r="L79" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="M79" s="12" t="s">
-        <v>185</v>
-      </c>
+      <c r="M79" s="12"/>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="12">
-        <v>28</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D80" s="12" t="s">
+      <c r="A80" s="63"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F80" s="13">
-        <v>46241</v>
+      <c r="E80" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G80" s="13">
         <v>46386</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I80" s="12" t="s">
+      <c r="H80" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80" s="14" t="s">
         <v>19</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L80" s="14" t="s">
         <v>52</v>
@@ -5038,57 +5163,57 @@
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="12">
+      <c r="A81" s="61">
         <v>28</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>24</v>
+        <v>188</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F81" s="13">
         <v>46241</v>
       </c>
       <c r="G81" s="13">
-        <v>46386</v>
+        <v>46249</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J81" s="12" t="s">
-        <v>26</v>
+      <c r="J81" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L81" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="M81" s="12"/>
+      <c r="M81" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="12">
-        <v>28</v>
-      </c>
+      <c r="A82" s="62"/>
       <c r="B82" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>24</v>
@@ -5109,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L82" s="14" t="s">
         <v>52</v>
@@ -5118,17 +5243,15 @@
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="12">
-        <v>28</v>
-      </c>
+      <c r="A83" s="62"/>
       <c r="B83" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>24</v>
@@ -5149,7 +5272,7 @@
         <v>26</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L83" s="14" t="s">
         <v>52</v>
@@ -5158,80 +5281,74 @@
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="12">
-        <v>28</v>
-      </c>
+      <c r="A84" s="62"/>
       <c r="B84" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>191</v>
+        <v>171</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>192</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="F84" s="13">
         <v>46241</v>
       </c>
       <c r="G84" s="13">
-        <v>46265</v>
+        <v>46386</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I84" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="L84" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="M84" s="12" t="s">
-        <v>194</v>
-      </c>
+      <c r="M84" s="12"/>
       <c r="N84" s="12"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="12">
-        <v>29</v>
-      </c>
+      <c r="A85" s="63"/>
       <c r="B85" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>191</v>
+        <v>171</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="F85" s="13">
         <v>46241</v>
       </c>
       <c r="G85" s="13">
-        <v>46265</v>
+        <v>46386</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I85" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="L85" s="14" t="s">
         <v>52</v>
@@ -5244,72 +5361,76 @@
         <v>29</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C86" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="E86" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="13">
+        <v>46241</v>
+      </c>
+      <c r="G86" s="13">
+        <v>46265</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K86" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="E86" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13">
-        <v>46233</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K86" s="12" t="s">
-        <v>193</v>
-      </c>
       <c r="L86" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M86" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="M86" s="12" t="s">
+        <v>198</v>
+      </c>
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>195</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="E87" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>25</v>
+      <c r="E87" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" s="13">
+        <v>46241</v>
       </c>
       <c r="G87" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L87" s="14" t="s">
         <v>52</v>
@@ -5319,25 +5440,23 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E88" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F88" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="F88" s="13"/>
       <c r="G88" s="13">
-        <v>46386</v>
+        <v>46295</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>24</v>
@@ -5349,10 +5468,10 @@
         <v>50</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L88" s="14" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="M88" s="12"/>
       <c r="N88" s="12"/>
@@ -5362,13 +5481,13 @@
         <v>31</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>202</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>24</v>
@@ -5389,7 +5508,7 @@
         <v>50</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L89" s="14" t="s">
         <v>52</v>
@@ -5402,13 +5521,13 @@
         <v>31</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>24</v>
@@ -5429,7 +5548,7 @@
         <v>50</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L90" s="14" t="s">
         <v>52</v>
@@ -5437,42 +5556,90 @@
       <c r="M90" s="12"/>
       <c r="N90" s="12"/>
     </row>
-    <row r="126" spans="1:14">
-      <c r="A126" s="39"/>
-      <c r="B126"/>
-      <c r="C126" s="39"/>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-      <c r="I126"/>
-      <c r="J126"/>
-      <c r="K126"/>
-      <c r="L126"/>
-      <c r="M126"/>
-      <c r="N126"/>
-    </row>
-    <row r="127" spans="1:14">
-      <c r="A127" s="39"/>
-      <c r="B127"/>
-      <c r="C127" s="39"/>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
-      <c r="I127"/>
-      <c r="J127"/>
-      <c r="K127"/>
-      <c r="L127"/>
-      <c r="M127"/>
-      <c r="N127"/>
+    <row r="91" spans="1:14">
+      <c r="A91" s="12">
+        <v>31</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" s="13">
+        <v>46386</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="L91" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="12">
+        <v>31</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" s="13">
+        <v>46386</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K92" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="L92" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
     </row>
     <row r="128" spans="1:14">
-      <c r="A128" s="39"/>
+      <c r="A128" s="65"/>
       <c r="B128"/>
-      <c r="C128" s="39"/>
+      <c r="C128" s="65"/>
       <c r="D128"/>
       <c r="E128"/>
       <c r="F128"/>
@@ -5486,9 +5653,9 @@
       <c r="N128"/>
     </row>
     <row r="129" spans="1:14">
-      <c r="A129" s="39"/>
+      <c r="A129" s="65"/>
       <c r="B129"/>
-      <c r="C129" s="39"/>
+      <c r="C129" s="65"/>
       <c r="D129"/>
       <c r="E129"/>
       <c r="F129"/>
@@ -5502,9 +5669,9 @@
       <c r="N129"/>
     </row>
     <row r="130" spans="1:14">
-      <c r="A130" s="39"/>
+      <c r="A130" s="65"/>
       <c r="B130"/>
-      <c r="C130" s="39"/>
+      <c r="C130" s="65"/>
       <c r="D130"/>
       <c r="E130"/>
       <c r="F130"/>
@@ -5518,9 +5685,9 @@
       <c r="N130"/>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="39"/>
+      <c r="A131" s="65"/>
       <c r="B131"/>
-      <c r="C131" s="39"/>
+      <c r="C131" s="65"/>
       <c r="D131"/>
       <c r="E131"/>
       <c r="F131"/>
@@ -5534,9 +5701,9 @@
       <c r="N131"/>
     </row>
     <row r="132" spans="1:14">
-      <c r="A132" s="39"/>
+      <c r="A132" s="65"/>
       <c r="B132"/>
-      <c r="C132" s="39"/>
+      <c r="C132" s="65"/>
       <c r="D132"/>
       <c r="E132"/>
       <c r="F132"/>
@@ -5550,9 +5717,9 @@
       <c r="N132"/>
     </row>
     <row r="133" spans="1:14">
-      <c r="A133" s="39"/>
+      <c r="A133" s="65"/>
       <c r="B133"/>
-      <c r="C133" s="39"/>
+      <c r="C133" s="65"/>
       <c r="D133"/>
       <c r="E133"/>
       <c r="F133"/>
@@ -5566,9 +5733,9 @@
       <c r="N133"/>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="39"/>
+      <c r="A134" s="65"/>
       <c r="B134"/>
-      <c r="C134" s="39"/>
+      <c r="C134" s="65"/>
       <c r="D134"/>
       <c r="E134"/>
       <c r="F134"/>
@@ -5582,9 +5749,9 @@
       <c r="N134"/>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="39"/>
+      <c r="A135" s="65"/>
       <c r="B135"/>
-      <c r="C135" s="39"/>
+      <c r="C135" s="65"/>
       <c r="D135"/>
       <c r="E135"/>
       <c r="F135"/>
@@ -5598,9 +5765,9 @@
       <c r="N135"/>
     </row>
     <row r="136" spans="1:14">
-      <c r="A136" s="39"/>
+      <c r="A136" s="65"/>
       <c r="B136"/>
-      <c r="C136" s="39"/>
+      <c r="C136" s="65"/>
       <c r="D136"/>
       <c r="E136"/>
       <c r="F136"/>
@@ -5614,9 +5781,9 @@
       <c r="N136"/>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="39"/>
+      <c r="A137" s="65"/>
       <c r="B137"/>
-      <c r="C137" s="39"/>
+      <c r="C137" s="65"/>
       <c r="D137"/>
       <c r="E137"/>
       <c r="F137"/>
@@ -5630,9 +5797,9 @@
       <c r="N137"/>
     </row>
     <row r="138" spans="1:14">
-      <c r="A138" s="39"/>
+      <c r="A138" s="65"/>
       <c r="B138"/>
-      <c r="C138" s="39"/>
+      <c r="C138" s="65"/>
       <c r="D138"/>
       <c r="E138"/>
       <c r="F138"/>
@@ -5646,9 +5813,9 @@
       <c r="N138"/>
     </row>
     <row r="139" spans="1:14">
-      <c r="A139" s="39"/>
+      <c r="A139" s="65"/>
       <c r="B139"/>
-      <c r="C139" s="39"/>
+      <c r="C139" s="65"/>
       <c r="D139"/>
       <c r="E139"/>
       <c r="F139"/>
@@ -5662,9 +5829,9 @@
       <c r="N139"/>
     </row>
     <row r="140" spans="1:14">
-      <c r="A140" s="39"/>
+      <c r="A140" s="65"/>
       <c r="B140"/>
-      <c r="C140" s="39"/>
+      <c r="C140" s="65"/>
       <c r="D140"/>
       <c r="E140"/>
       <c r="F140"/>
@@ -5678,9 +5845,9 @@
       <c r="N140"/>
     </row>
     <row r="141" spans="1:14">
-      <c r="A141" s="39"/>
+      <c r="A141" s="65"/>
       <c r="B141"/>
-      <c r="C141" s="39"/>
+      <c r="C141" s="65"/>
       <c r="D141"/>
       <c r="E141"/>
       <c r="F141"/>
@@ -5694,9 +5861,9 @@
       <c r="N141"/>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="39"/>
+      <c r="A142" s="65"/>
       <c r="B142"/>
-      <c r="C142" s="39"/>
+      <c r="C142" s="65"/>
       <c r="D142"/>
       <c r="E142"/>
       <c r="F142"/>
@@ -5710,9 +5877,9 @@
       <c r="N142"/>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="39"/>
+      <c r="A143" s="65"/>
       <c r="B143"/>
-      <c r="C143" s="39"/>
+      <c r="C143" s="65"/>
       <c r="D143"/>
       <c r="E143"/>
       <c r="F143"/>
@@ -5726,9 +5893,9 @@
       <c r="N143"/>
     </row>
     <row r="144" spans="1:14">
-      <c r="A144" s="39"/>
+      <c r="A144" s="65"/>
       <c r="B144"/>
-      <c r="C144" s="39"/>
+      <c r="C144" s="65"/>
       <c r="D144"/>
       <c r="E144"/>
       <c r="F144"/>
@@ -5742,9 +5909,9 @@
       <c r="N144"/>
     </row>
     <row r="145" spans="1:14">
-      <c r="A145" s="39"/>
+      <c r="A145" s="65"/>
       <c r="B145"/>
-      <c r="C145" s="39"/>
+      <c r="C145" s="65"/>
       <c r="D145"/>
       <c r="E145"/>
       <c r="F145"/>
@@ -5758,9 +5925,9 @@
       <c r="N145"/>
     </row>
     <row r="146" spans="1:14">
-      <c r="A146" s="39"/>
+      <c r="A146" s="65"/>
       <c r="B146"/>
-      <c r="C146" s="39"/>
+      <c r="C146" s="65"/>
       <c r="D146"/>
       <c r="E146"/>
       <c r="F146"/>
@@ -5774,9 +5941,9 @@
       <c r="N146"/>
     </row>
     <row r="147" spans="1:14">
-      <c r="A147" s="39"/>
+      <c r="A147" s="65"/>
       <c r="B147"/>
-      <c r="C147" s="39"/>
+      <c r="C147" s="65"/>
       <c r="D147"/>
       <c r="E147"/>
       <c r="F147"/>
@@ -5790,9 +5957,9 @@
       <c r="N147"/>
     </row>
     <row r="148" spans="1:14">
-      <c r="A148" s="39"/>
+      <c r="A148" s="65"/>
       <c r="B148"/>
-      <c r="C148" s="39"/>
+      <c r="C148" s="65"/>
       <c r="D148"/>
       <c r="E148"/>
       <c r="F148"/>
@@ -5806,9 +5973,9 @@
       <c r="N148"/>
     </row>
     <row r="149" spans="1:14">
-      <c r="A149" s="39"/>
+      <c r="A149" s="65"/>
       <c r="B149"/>
-      <c r="C149" s="39"/>
+      <c r="C149" s="65"/>
       <c r="D149"/>
       <c r="E149"/>
       <c r="F149"/>
@@ -5822,9 +5989,9 @@
       <c r="N149"/>
     </row>
     <row r="150" spans="1:14">
-      <c r="A150" s="39"/>
+      <c r="A150" s="65"/>
       <c r="B150"/>
-      <c r="C150" s="39"/>
+      <c r="C150" s="65"/>
       <c r="D150"/>
       <c r="E150"/>
       <c r="F150"/>
@@ -5838,9 +6005,9 @@
       <c r="N150"/>
     </row>
     <row r="151" spans="1:14">
-      <c r="A151" s="39"/>
+      <c r="A151" s="65"/>
       <c r="B151"/>
-      <c r="C151" s="39"/>
+      <c r="C151" s="65"/>
       <c r="D151"/>
       <c r="E151"/>
       <c r="F151"/>
@@ -5854,9 +6021,9 @@
       <c r="N151"/>
     </row>
     <row r="152" spans="1:14">
-      <c r="A152" s="39"/>
+      <c r="A152" s="65"/>
       <c r="B152"/>
-      <c r="C152" s="39"/>
+      <c r="C152" s="65"/>
       <c r="D152"/>
       <c r="E152"/>
       <c r="F152"/>
@@ -5870,9 +6037,9 @@
       <c r="N152"/>
     </row>
     <row r="153" spans="1:14">
-      <c r="A153" s="39"/>
+      <c r="A153" s="65"/>
       <c r="B153"/>
-      <c r="C153" s="39"/>
+      <c r="C153" s="65"/>
       <c r="D153"/>
       <c r="E153"/>
       <c r="F153"/>
@@ -5886,9 +6053,9 @@
       <c r="N153"/>
     </row>
     <row r="154" spans="1:14">
-      <c r="A154" s="39"/>
+      <c r="A154" s="65"/>
       <c r="B154"/>
-      <c r="C154" s="39"/>
+      <c r="C154" s="65"/>
       <c r="D154"/>
       <c r="E154"/>
       <c r="F154"/>
@@ -5902,9 +6069,9 @@
       <c r="N154"/>
     </row>
     <row r="155" spans="1:14">
-      <c r="A155" s="39"/>
+      <c r="A155" s="65"/>
       <c r="B155"/>
-      <c r="C155" s="39"/>
+      <c r="C155" s="65"/>
       <c r="D155"/>
       <c r="E155"/>
       <c r="F155"/>
@@ -5918,9 +6085,9 @@
       <c r="N155"/>
     </row>
     <row r="156" spans="1:14">
-      <c r="A156" s="39"/>
+      <c r="A156" s="65"/>
       <c r="B156"/>
-      <c r="C156" s="39"/>
+      <c r="C156" s="65"/>
       <c r="D156"/>
       <c r="E156"/>
       <c r="F156"/>
@@ -5933,17 +6100,48 @@
       <c r="M156"/>
       <c r="N156"/>
     </row>
+    <row r="157" spans="1:14">
+      <c r="A157" s="65"/>
+      <c r="B157"/>
+      <c r="C157" s="65"/>
+      <c r="D157"/>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157"/>
+      <c r="I157"/>
+      <c r="J157"/>
+      <c r="K157"/>
+      <c r="L157"/>
+      <c r="M157"/>
+      <c r="N157"/>
+    </row>
+    <row r="158" spans="1:14">
+      <c r="A158" s="65"/>
+      <c r="B158"/>
+      <c r="C158" s="65"/>
+      <c r="D158"/>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
+      <c r="K158"/>
+      <c r="L158"/>
+      <c r="M158"/>
+      <c r="N158"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="56">
+  <mergeCells count="59">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A37"/>
@@ -5953,29 +6151,31 @@
     <mergeCell ref="A49:A53"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A89:A92"/>
     <mergeCell ref="B3:B10"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B16:B27"/>
     <mergeCell ref="B28:B33"/>
     <mergeCell ref="B34:B58"/>
-    <mergeCell ref="B59:B67"/>
-    <mergeCell ref="B68:B83"/>
-    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B59:B69"/>
+    <mergeCell ref="B70:B85"/>
+    <mergeCell ref="B86:B92"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C27"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="C34:C38"/>
@@ -5985,16 +6185,18 @@
     <mergeCell ref="C49:C53"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C59:C66"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="C87:C90"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="C73:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C89:C92"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66 H1:H58 H59:H60 H61:H62 H63:H65 H67:H68 H69:H1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>

--- a/source/人工智能场景计划表-0810.xlsx
+++ b/source/人工智能场景计划表-0810.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="209">
   <si>
     <t>浙江电力交易中心人工智能场景建设计划表</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>随国家能源局项目开展</t>
+  </si>
+  <si>
+    <t>项目审查</t>
+  </si>
+  <si>
+    <t>重复立项审查</t>
   </si>
   <si>
     <t>政策解读智能辅助场景</t>
@@ -1196,7 +1202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1257,19 +1263,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1307,19 +1300,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1330,17 +1310,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1487,7 +1456,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1499,34 +1468,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1612,7 +1581,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1669,36 +1638,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1729,58 +1701,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1790,15 +1747,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1877,10 +1825,10 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0" dbFileVersion="0" changeLogVersion="0">
-    <open main="49" threadCnt="1"/>
+    <open main="40" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="1">
-        <open main="3" threadCnt="1"/>
+        <open main="2" threadCnt="1"/>
       </sheetInfo>
     </sheetInfos>
   </bookInfo>
@@ -2082,7 +2030,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -2202,7 +2150,7 @@
     </row>
     <row r="4" ht="28.5" spans="1:14">
       <c r="A4" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>15</v>
@@ -2244,7 +2192,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>15</v>
@@ -2284,7 +2232,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>15</v>
@@ -2324,7 +2272,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>15</v>
@@ -2364,7 +2312,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>15</v>
@@ -2404,7 +2352,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>15</v>
@@ -2444,7 +2392,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>15</v>
@@ -2483,13 +2431,13 @@
       <c r="N10" s="12"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:14">
-      <c r="A11" s="20">
-        <v>3</v>
+      <c r="A11" s="12">
+        <v>9</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="12" t="s">
@@ -2525,9 +2473,11 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" customFormat="1" spans="1:14">
-      <c r="A12" s="22"/>
+      <c r="A12" s="12">
+        <v>10</v>
+      </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="23"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="12" t="s">
         <v>41</v>
       </c>
@@ -2558,62 +2508,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" customFormat="1" spans="1:14">
       <c r="A13" s="12">
-        <v>4</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F13" s="13"/>
       <c r="G13" s="13">
-        <v>46249</v>
+        <v>46325</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="12" t="s">
-        <v>47</v>
-      </c>
+      <c r="M13" s="12"/>
       <c r="N13" s="12"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" ht="19.5" customHeight="1" spans="1:14">
       <c r="A14" s="12">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>48</v>
+      <c r="C14" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="13" t="s">
@@ -2626,32 +2570,34 @@
         <v>19</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="12">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>48</v>
+      <c r="C15" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>18</v>
@@ -2669,70 +2615,78 @@
         <v>24</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="12"/>
-      <c r="B16" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="A16" s="12">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>24</v>
+      <c r="E16" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="13">
-        <v>46386</v>
+        <v>46249</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>22</v>
+        <v>53</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
     </row>
-    <row r="17" ht="28.5" spans="1:14">
-      <c r="A17" s="12"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="25" t="s">
+    <row r="17" spans="1:14">
+      <c r="A17" s="12">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="13">
-        <v>46234</v>
+      <c r="E17" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G17" s="13">
-        <v>46295</v>
+        <v>46386</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>24</v>
@@ -2744,33 +2698,31 @@
         <v>26</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" ht="28.5" spans="1:14">
+      <c r="A18" s="12">
+        <v>16</v>
+      </c>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="12"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="28" t="s">
+      <c r="E18" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>25</v>
+      <c r="F18" s="13">
+        <v>46234</v>
       </c>
       <c r="G18" s="13">
-        <v>46386</v>
+        <v>46295</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>24</v>
@@ -2782,20 +2734,26 @@
         <v>26</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="12"/>
+      <c r="M18" s="23" t="s">
+        <v>62</v>
+      </c>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="12"/>
+      <c r="A19" s="12">
+        <v>17</v>
+      </c>
       <c r="B19" s="26"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="28" t="s">
         <v>63</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>64</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>24</v>
@@ -2810,13 +2768,13 @@
         <v>24</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L19" s="14" t="s">
         <v>22</v>
@@ -2825,11 +2783,13 @@
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="12"/>
+      <c r="A20" s="12">
+        <v>18</v>
+      </c>
       <c r="B20" s="26"/>
       <c r="C20" s="29"/>
-      <c r="D20" s="12" t="s">
-        <v>64</v>
+      <c r="D20" s="23" t="s">
+        <v>65</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>24</v>
@@ -2850,7 +2810,7 @@
         <v>26</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L20" s="14" t="s">
         <v>22</v>
@@ -2859,11 +2819,13 @@
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="12"/>
+      <c r="A21" s="12">
+        <v>19</v>
+      </c>
       <c r="B21" s="26"/>
       <c r="C21" s="29"/>
       <c r="D21" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>24</v>
@@ -2878,13 +2840,13 @@
         <v>24</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L21" s="14" t="s">
         <v>22</v>
@@ -2894,12 +2856,10 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="12">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B22" s="26"/>
-      <c r="C22" s="18" t="s">
-        <v>66</v>
-      </c>
+      <c r="C22" s="29"/>
       <c r="D22" s="12" t="s">
         <v>67</v>
       </c>
@@ -2910,19 +2870,19 @@
         <v>25</v>
       </c>
       <c r="G22" s="13">
-        <v>46326</v>
+        <v>46386</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L22" s="14" t="s">
         <v>22</v>
@@ -2932,11 +2892,11 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="12">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B23" s="26"/>
-      <c r="C23" s="19" t="s">
-        <v>66</v>
+      <c r="C23" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>69</v>
@@ -2948,7 +2908,7 @@
         <v>25</v>
       </c>
       <c r="G23" s="13">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>24</v>
@@ -2960,7 +2920,7 @@
         <v>26</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L23" s="14" t="s">
         <v>22</v>
@@ -2969,10 +2929,12 @@
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="26"/>
+      <c r="A24" s="12">
+        <v>22</v>
+      </c>
       <c r="B24" s="26"/>
-      <c r="C24" s="26" t="s">
-        <v>70</v>
+      <c r="C24" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>71</v>
@@ -2984,7 +2946,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>24</v>
@@ -2993,10 +2955,10 @@
         <v>19</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L24" s="14" t="s">
         <v>22</v>
@@ -3005,32 +2967,36 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="22"/>
+      <c r="A25" s="12">
+        <v>23</v>
+      </c>
       <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+      <c r="C25" s="26" t="s">
+        <v>72</v>
+      </c>
       <c r="D25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="13">
-        <v>46233</v>
+      <c r="E25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G25" s="13">
         <v>46386</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L25" s="14" t="s">
         <v>22</v>
@@ -3039,23 +3005,25 @@
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="22"/>
+      <c r="A26" s="12">
+        <v>24</v>
+      </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
-      <c r="D26" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>25</v>
+      <c r="D26" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="13">
+        <v>46233</v>
       </c>
       <c r="G26" s="13">
         <v>46386</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>19</v>
@@ -3064,7 +3032,7 @@
         <v>26</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L26" s="14" t="s">
         <v>22</v>
@@ -3073,11 +3041,13 @@
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="25" t="s">
-        <v>75</v>
+      <c r="A27" s="12">
+        <v>25</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="23" t="s">
+        <v>76</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>24</v>
@@ -3098,7 +3068,7 @@
         <v>26</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L27" s="14" t="s">
         <v>22</v>
@@ -3106,27 +3076,23 @@
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
     </row>
-    <row r="28" ht="28.5" spans="1:14">
+    <row r="28" spans="1:14">
       <c r="A28" s="12">
-        <v>9</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="13">
-        <v>46241</v>
+      <c r="F28" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G28" s="13">
-        <v>46285</v>
+        <v>46386</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>24</v>
@@ -3134,68 +3100,68 @@
       <c r="I28" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="14" t="s">
+      <c r="J28" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="L28" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" ht="28.5" spans="1:14">
+      <c r="A29" s="12">
+        <v>27</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="12">
-        <v>10</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="E29" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>25</v>
+      <c r="F29" s="13">
+        <v>46241</v>
       </c>
       <c r="G29" s="13">
-        <v>46387</v>
+        <v>46285</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J29" s="14" t="s">
         <v>26</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L29" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="12"/>
+      <c r="M29" s="12" t="s">
+        <v>82</v>
+      </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="12">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>83</v>
       </c>
       <c r="D30" s="12" t="s">
@@ -3216,34 +3182,32 @@
       <c r="I30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="14" t="s">
         <v>26</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L30" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N30" s="30"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="12">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>85</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="13" t="s">
@@ -3259,50 +3223,52 @@
         <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L31" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
+      <c r="M31" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="N31" s="31"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="12">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>87</v>
+        <v>78</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="13">
-        <v>46234</v>
+        <v>24</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G32" s="13">
-        <v>46241</v>
+        <v>46387</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L32" s="14" t="s">
         <v>22</v>
@@ -3312,16 +3278,16 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="12">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>18</v>
@@ -3342,7 +3308,7 @@
         <v>26</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L33" s="14" t="s">
         <v>22</v>
@@ -3352,25 +3318,25 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="12">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>93</v>
+      <c r="F34" s="13">
+        <v>46234</v>
+      </c>
+      <c r="G34" s="13">
+        <v>46241</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>19</v>
@@ -3378,144 +3344,148 @@
       <c r="I34" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>94</v>
+      <c r="J34" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
     </row>
-    <row r="35" ht="28.5" spans="1:14">
+    <row r="35" spans="1:14">
       <c r="A35" s="12">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K35" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="13" t="s">
+      <c r="L35" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K35" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M35" s="32" t="s">
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" ht="28.5" spans="1:14">
+      <c r="A36" s="12">
+        <v>34</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="N35" s="32"/>
-    </row>
-    <row r="36" ht="71.25" spans="1:14">
-      <c r="A36" s="12">
-        <v>13</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="31" t="s">
-        <v>100</v>
-      </c>
       <c r="E36" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L36" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M36" s="32" t="s">
+      <c r="M36" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="N36" s="33" t="s">
+      <c r="N36" s="33"/>
+    </row>
+    <row r="37" ht="71.25" spans="1:14">
+      <c r="A37" s="12">
+        <v>35</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="32" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="37" ht="28.5" spans="1:14">
-      <c r="A37" s="12">
-        <v>13</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="E37" s="12" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G37" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L37" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M37" s="34"/>
-      <c r="N37" s="32" t="s">
+      <c r="M37" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="N37" s="34" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="22"/>
+    <row r="38" ht="28.5" spans="1:14">
+      <c r="A38" s="12">
+        <v>36</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="26"/>
       <c r="D38" s="12" t="s">
         <v>105</v>
       </c>
@@ -3526,168 +3496,164 @@
         <v>25</v>
       </c>
       <c r="G38" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L38" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H38" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="33" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="12">
-        <v>14</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>106</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F39" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="13">
-        <v>46241</v>
+      <c r="G39" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I39" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M39" s="12"/>
-      <c r="N39" s="12" t="s">
-        <v>109</v>
-      </c>
+      <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="12">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G40" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="13">
+        <v>46241</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K40" s="12" t="s">
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="12">
+        <v>39</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="L40" s="14" t="s">
+      <c r="D41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-    </row>
-    <row r="41" ht="66" spans="1:14">
-      <c r="A41" s="12">
-        <v>15</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="13">
-        <v>46254</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>94</v>
-      </c>
       <c r="K41" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+    </row>
+    <row r="42" ht="66" spans="1:14">
+      <c r="A42" s="12">
+        <v>40</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M41" s="12"/>
-      <c r="N41" s="31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" ht="33" spans="1:14">
-      <c r="A42" s="12">
-        <v>15</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="G42" s="13">
         <v>46254</v>
@@ -3699,39 +3665,37 @@
         <v>19</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L42" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M42" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="M42" s="12"/>
+      <c r="N42" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="N42" s="33" t="s">
+    </row>
+    <row r="43" ht="33" spans="1:14">
+      <c r="A43" s="12">
+        <v>41</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="32" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:14">
-      <c r="A43" s="12">
-        <v>15</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>18</v>
+      <c r="E43" s="32" t="s">
+        <v>61</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G43" s="13">
         <v>46254</v>
@@ -3743,270 +3707,278 @@
         <v>19</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L43" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M43" s="33"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" ht="42.75" spans="1:14">
+        <v>98</v>
+      </c>
+      <c r="M43" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="N43" s="34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:14">
       <c r="A44" s="12">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>120</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G44" s="13">
+        <v>46254</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M44" s="34"/>
+      <c r="N44" s="12"/>
+    </row>
+    <row r="45" ht="42.75" spans="1:14">
+      <c r="A45" s="12">
+        <v>43</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="12" t="s">
+      <c r="E45" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M44" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="12" t="s">
+      <c r="K45" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M45" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E45" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" s="13">
-        <v>46265</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L45" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" ht="28.5" spans="1:14">
-      <c r="A46" s="12"/>
+      <c r="N45" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="12">
+        <v>44</v>
+      </c>
       <c r="B46" s="12"/>
       <c r="C46" s="19"/>
       <c r="D46" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="36" t="s">
         <v>25</v>
       </c>
       <c r="G46" s="13">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L46" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="L46" s="14" t="s">
         <v>22</v>
       </c>
       <c r="M46" s="12"/>
-      <c r="N46" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="N46" s="12"/>
+    </row>
+    <row r="47" ht="28.5" spans="1:14">
       <c r="A47" s="12">
-        <v>16</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>119</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="19"/>
       <c r="D47" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>121</v>
+      <c r="F47" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="13">
+        <v>46252</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L47" s="14" t="s">
-        <v>52</v>
+        <v>97</v>
+      </c>
+      <c r="L47" s="37" t="s">
+        <v>22</v>
       </c>
       <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" ht="28.5" spans="1:14">
+      <c r="N47" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="12">
-        <v>17</v>
-      </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>130</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48" s="13">
-        <v>46386</v>
+        <v>123</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L48" s="36" t="s">
-        <v>22</v>
+        <v>97</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" ht="16.5" spans="1:14">
+    <row r="49" ht="28.5" spans="1:14">
       <c r="A49" s="12">
-        <v>18</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B49" s="12"/>
       <c r="C49" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="31" t="s">
+      <c r="D49" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>18</v>
+      <c r="E49" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>134</v>
+        <v>25</v>
+      </c>
+      <c r="G49" s="13">
+        <v>46386</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>24</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="L49" s="36" t="s">
-        <v>52</v>
+        <v>97</v>
+      </c>
+      <c r="L49" s="37" t="s">
+        <v>22</v>
       </c>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
     </row>
     <row r="50" ht="16.5" spans="1:14">
       <c r="A50" s="12">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>134</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>19</v>
@@ -4018,61 +3990,67 @@
         <v>20</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="L50" s="36" t="s">
-        <v>52</v>
+        <v>110</v>
+      </c>
+      <c r="L50" s="37" t="s">
+        <v>54</v>
       </c>
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12" t="s">
+    <row r="51" ht="16.5" spans="1:14">
+      <c r="A51" s="12">
+        <v>49</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E51" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" s="13">
-        <v>46386</v>
-      </c>
       <c r="H51" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L51" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M51" s="32" t="s">
-        <v>137</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="L51" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="12"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" ht="28.5" spans="1:14">
-      <c r="A52" s="12"/>
+    <row r="52" spans="1:14">
+      <c r="A52" s="12">
+        <v>50</v>
+      </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="12" t="s">
         <v>138</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="36" t="s">
         <v>25</v>
       </c>
       <c r="G52" s="13">
@@ -4088,49 +4066,45 @@
         <v>26</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L52" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12" t="s">
+      <c r="M52" s="33" t="s">
         <v>139</v>
       </c>
+      <c r="N52" s="12"/>
     </row>
     <row r="53" ht="28.5" spans="1:14">
       <c r="A53" s="12">
-        <v>17</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>134</v>
+      <c r="E53" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="13">
+        <v>46386</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L53" s="14" t="s">
         <v>22</v>
@@ -4142,55 +4116,55 @@
     </row>
     <row r="54" ht="28.5" spans="1:14">
       <c r="A54" s="12">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C54" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="E54" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L54" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="E54" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" s="13">
-        <v>46386</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K54" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L54" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M54" s="12" t="s">
+    </row>
+    <row r="55" ht="28.5" spans="1:14">
+      <c r="A55" s="12">
+        <v>53</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="N54" s="12"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="12">
-        <v>19</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>145</v>
@@ -4211,29 +4185,31 @@
         <v>19</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L55" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M55" s="12"/>
+        <v>98</v>
+      </c>
+      <c r="M55" s="12" t="s">
+        <v>146</v>
+      </c>
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="12">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -4251,26 +4227,26 @@
         <v>19</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L56" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
     </row>
-    <row r="57" ht="57" spans="1:14">
+    <row r="57" spans="1:14">
       <c r="A57" s="12">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" s="37" t="s">
-        <v>147</v>
+        <v>92</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>148</v>
@@ -4281,43 +4257,39 @@
       <c r="F57" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="13">
+        <v>46386</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L57" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+    </row>
+    <row r="58" ht="57" spans="1:14">
+      <c r="A58" s="12">
+        <v>56</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C58" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="H57" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" s="12" t="s">
+      <c r="D58" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L57" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M57" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="20">
-        <v>21</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>24</v>
@@ -4326,77 +4298,87 @@
         <v>25</v>
       </c>
       <c r="G58" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="12">
+        <v>57</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="H58" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L58" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="39">
-        <v>21</v>
-      </c>
-      <c r="B59" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="C59" s="41" t="s">
+      <c r="D59" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="35" t="s">
+      <c r="E59" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G59" s="13">
-        <v>46249</v>
+      <c r="G59" s="13" t="s">
+        <v>151</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="23" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="43"/>
-      <c r="B60" s="44"/>
-      <c r="C60" s="41"/>
+      <c r="A60" s="12">
+        <v>58</v>
+      </c>
+      <c r="B60" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>157</v>
+      </c>
       <c r="D60" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="36" t="s">
+      <c r="E60" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="F60" s="35" t="s">
+      <c r="F60" s="36" t="s">
         <v>25</v>
       </c>
       <c r="G60" s="13">
@@ -4412,199 +4394,209 @@
         <v>20</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L60" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="39">
-        <v>22</v>
-      </c>
-      <c r="B61" s="44"/>
-      <c r="C61" s="45" t="s">
+      <c r="A61" s="12">
+        <v>59</v>
+      </c>
+      <c r="B61" s="43"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="13">
+        <v>46249</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D61" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="F61" s="48">
-        <v>46234</v>
-      </c>
-      <c r="G61" s="48">
-        <v>46241</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="L61" s="49" t="s">
-        <v>52</v>
+      <c r="L61" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="50"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="46" t="s">
+      <c r="A62" s="12">
+        <v>60</v>
+      </c>
+      <c r="B62" s="43"/>
+      <c r="C62" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="47" t="s">
+      <c r="D62" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E62" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="47">
         <v>46234</v>
       </c>
-      <c r="G62" s="48">
-        <v>46265</v>
+      <c r="G62" s="47">
+        <v>46241</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I62" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62" s="47" t="s">
+      <c r="I62" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="L62" s="49" t="s">
-        <v>52</v>
+      <c r="K62" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="L62" s="48" t="s">
+        <v>54</v>
       </c>
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="50"/>
-      <c r="B63" s="44"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F63" s="48">
+      <c r="A63" s="12">
+        <v>61</v>
+      </c>
+      <c r="B63" s="43"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="47">
         <v>46234</v>
       </c>
-      <c r="G63" s="48">
+      <c r="G63" s="47">
         <v>46265</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I63" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" s="47" t="s">
+      <c r="I63" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="L63" s="49" t="s">
-        <v>52</v>
+      <c r="K63" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="L63" s="48" t="s">
+        <v>54</v>
       </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="50"/>
-      <c r="B64" s="44"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" s="48">
+      <c r="A64" s="12">
+        <v>62</v>
+      </c>
+      <c r="B64" s="43"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="E64" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="47">
         <v>46234</v>
       </c>
-      <c r="G64" s="48">
+      <c r="G64" s="47">
         <v>46265</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="K64" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="L64" s="49" t="s">
-        <v>52</v>
+      <c r="K64" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="L64" s="48" t="s">
+        <v>54</v>
       </c>
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="50"/>
-      <c r="B65" s="44"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="E65" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="13">
+      <c r="A65" s="12">
+        <v>63</v>
+      </c>
+      <c r="B65" s="43"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" s="47">
+        <v>46234</v>
+      </c>
+      <c r="G65" s="47">
         <v>46265</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I65" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" s="47" t="s">
+      <c r="I65" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="K65" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="L65" s="49" t="s">
-        <v>52</v>
+      <c r="K65" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="L65" s="48" t="s">
+        <v>54</v>
       </c>
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="43"/>
-      <c r="B66" s="44"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" s="35" t="s">
+      <c r="A66" s="12">
+        <v>64</v>
+      </c>
+      <c r="B66" s="43"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" s="36" t="s">
         <v>25</v>
       </c>
       <c r="G66" s="13">
@@ -4613,40 +4605,38 @@
       <c r="H66" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66" s="12" t="s">
+      <c r="I66" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="K66" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="L66" s="14" t="s">
-        <v>52</v>
+      <c r="K66" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="L66" s="48" t="s">
+        <v>54</v>
       </c>
       <c r="M66" s="12"/>
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="39">
-        <v>23</v>
-      </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D67" s="52" t="s">
+      <c r="A67" s="12">
+        <v>65</v>
+      </c>
+      <c r="B67" s="43"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="E67" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="13">
-        <v>46234</v>
+      <c r="E67" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="G67" s="13">
-        <v>46386</v>
+        <v>46265</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>24</v>
@@ -4658,20 +4648,24 @@
         <v>20</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="43"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="52" t="s">
+      <c r="A68" s="12">
+        <v>66</v>
+      </c>
+      <c r="B68" s="43"/>
+      <c r="C68" s="41" t="s">
         <v>168</v>
+      </c>
+      <c r="D68" s="50" t="s">
+        <v>169</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>24</v>
@@ -4692,102 +4686,100 @@
         <v>20</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L68" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" ht="16.95" customHeight="1" spans="1:14">
-      <c r="A69" s="55">
-        <v>24</v>
-      </c>
-      <c r="B69" s="56"/>
-      <c r="C69" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="D69" s="12" t="s">
+    <row r="69" spans="1:14">
+      <c r="A69" s="12">
+        <v>67</v>
+      </c>
+      <c r="B69" s="43"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="13">
+        <v>46234</v>
+      </c>
+      <c r="G69" s="13">
+        <v>46386</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+    </row>
+    <row r="70" ht="16.95" customHeight="1" spans="1:14">
+      <c r="A70" s="12">
+        <v>68</v>
+      </c>
+      <c r="B70" s="52"/>
+      <c r="C70" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F69" s="13" t="s">
+      <c r="E70" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G69" s="13" t="s">
+      <c r="G70" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H69" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I69" s="12" t="s">
+      <c r="H70" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J69" s="12" t="s">
+      <c r="J70" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K70" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L69" s="14" t="s">
+      <c r="L70" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M69" s="12"/>
-      <c r="N69" s="25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="70" ht="27" spans="1:14">
-      <c r="A70" s="22">
-        <v>25</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C70" s="58" t="s">
+      <c r="M70" s="12"/>
+      <c r="N70" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D70" s="14" t="s">
+    </row>
+    <row r="71" ht="27" spans="1:14">
+      <c r="A71" s="12">
+        <v>69</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="E70" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" s="13">
-        <v>46241</v>
-      </c>
-      <c r="G70" s="13">
-        <v>46265</v>
-      </c>
-      <c r="H70" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K70" s="12" t="s">
+      <c r="C71" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="L70" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12"/>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" s="12">
-        <v>25</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C71" s="59"/>
       <c r="D71" s="14" t="s">
         <v>175</v>
       </c>
@@ -4803,34 +4795,34 @@
       <c r="H71" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I71" s="14" t="s">
         <v>24</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L71" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="12">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C72" s="60"/>
-      <c r="D72" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C72" s="55"/>
+      <c r="D72" s="14" t="s">
+        <v>177</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F72" s="13">
         <v>46241</v>
@@ -4839,7 +4831,7 @@
         <v>46265</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>24</v>
@@ -4848,35 +4840,33 @@
         <v>26</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L72" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M72" s="12"/>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="12">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>177</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C73" s="56"/>
       <c r="D73" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E73" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>25</v>
+      <c r="E73" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="13">
+        <v>46241</v>
       </c>
       <c r="G73" s="13">
-        <v>46325</v>
+        <v>46265</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>24</v>
@@ -4888,26 +4878,26 @@
         <v>26</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L73" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M73" s="12"/>
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="12">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>24</v>
@@ -4928,26 +4918,26 @@
         <v>26</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L74" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M74" s="12"/>
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="12">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>24</v>
@@ -4968,26 +4958,26 @@
         <v>26</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L75" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="12">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>24</v>
@@ -5008,23 +4998,23 @@
         <v>26</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L76" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="61">
-        <v>27</v>
+      <c r="A77" s="12">
+        <v>75</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>182</v>
+        <v>173</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>183</v>
@@ -5036,34 +5026,38 @@
         <v>25</v>
       </c>
       <c r="G77" s="13">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="H77" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>26</v>
       </c>
       <c r="K77" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L77" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M77" s="12"/>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="62"/>
+      <c r="A78" s="12">
+        <v>76</v>
+      </c>
       <c r="B78" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C78" s="29"/>
+        <v>173</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>184</v>
+      </c>
       <c r="D78" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>24</v>
@@ -5084,22 +5078,24 @@
         <v>26</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L78" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="62"/>
+      <c r="A79" s="12">
+        <v>77</v>
+      </c>
       <c r="B79" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C79" s="29"/>
       <c r="D79" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>24</v>
@@ -5119,139 +5115,143 @@
       <c r="J79" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="14" t="s">
-        <v>174</v>
+      <c r="K79" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="L79" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M79" s="12"/>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="63"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="64"/>
-      <c r="D80" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E80" s="14" t="s">
+      <c r="A80" s="12">
+        <v>78</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="29"/>
+      <c r="D80" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G80" s="13">
-        <v>46386</v>
-      </c>
-      <c r="H80" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I80" s="14" t="s">
+        <v>46295</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="12" t="s">
-        <v>174</v>
+      <c r="K80" s="14" t="s">
+        <v>176</v>
       </c>
       <c r="L80" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M80" s="12"/>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="61">
-        <v>28</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D81" s="12" t="s">
+      <c r="A81" s="12">
+        <v>79</v>
+      </c>
+      <c r="B81" s="12"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F81" s="13">
-        <v>46241</v>
+        <v>24</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="G81" s="13">
-        <v>46249</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>20</v>
+        <v>46386</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L81" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M81" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="12">
+        <v>80</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="N81" s="12"/>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" s="62"/>
-      <c r="B82" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>187</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="E82" s="12" t="s">
-        <v>24</v>
+      <c r="E82" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F82" s="13">
         <v>46241</v>
       </c>
       <c r="G82" s="13">
-        <v>46386</v>
+        <v>46249</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I82" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J82" s="12" t="s">
-        <v>26</v>
+      <c r="J82" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L82" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M82" s="12"/>
+        <v>54</v>
+      </c>
+      <c r="M82" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="62"/>
+      <c r="A83" s="12">
+        <v>81</v>
+      </c>
       <c r="B83" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>24</v>
@@ -5272,24 +5272,26 @@
         <v>26</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L83" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M83" s="12"/>
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="62"/>
+      <c r="A84" s="12">
+        <v>82</v>
+      </c>
       <c r="B84" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -5310,24 +5312,26 @@
         <v>26</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L84" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M84" s="12"/>
       <c r="N84" s="12"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="63"/>
+      <c r="A85" s="12">
+        <v>83</v>
+      </c>
       <c r="B85" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>24</v>
@@ -5348,70 +5352,68 @@
         <v>26</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L85" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="12">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C86" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D86" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>18</v>
+      <c r="E86" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="F86" s="13">
         <v>46241</v>
       </c>
       <c r="G86" s="13">
-        <v>46265</v>
+        <v>46386</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="L86" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M86" s="12" t="s">
-        <v>198</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="M86" s="12"/>
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="12">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>197</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E87" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E87" s="23" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="13">
@@ -5427,63 +5429,67 @@
         <v>19</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L87" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M87" s="12"/>
+        <v>54</v>
+      </c>
+      <c r="M87" s="12" t="s">
+        <v>200</v>
+      </c>
       <c r="N87" s="12"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="12">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E88" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F88" s="13"/>
+      <c r="E88" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" s="13">
+        <v>46241</v>
+      </c>
       <c r="G88" s="13">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L88" s="14" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="M88" s="12"/>
       <c r="N88" s="12"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="12">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" s="12" t="s">
         <v>202</v>
       </c>
       <c r="D89" s="12" t="s">
@@ -5492,11 +5498,9 @@
       <c r="E89" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="F89" s="13"/>
       <c r="G89" s="13">
-        <v>46386</v>
+        <v>46295</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>24</v>
@@ -5505,29 +5509,29 @@
         <v>24</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L89" s="14" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="M89" s="12"/>
       <c r="N89" s="12"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="12">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>202</v>
+        <v>196</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>204</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>24</v>
@@ -5545,29 +5549,29 @@
         <v>24</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L90" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M90" s="12"/>
       <c r="N90" s="12"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="12">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>24</v>
@@ -5585,29 +5589,29 @@
         <v>24</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M91" s="12"/>
       <c r="N91" s="12"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="12">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>24</v>
@@ -5625,37 +5629,61 @@
         <v>24</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L92" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M92" s="12"/>
       <c r="N92" s="12"/>
     </row>
-    <row r="128" spans="1:14">
-      <c r="A128" s="65"/>
-      <c r="B128"/>
-      <c r="C128" s="65"/>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
-      <c r="J128"/>
-      <c r="K128"/>
-      <c r="L128"/>
-      <c r="M128"/>
-      <c r="N128"/>
+    <row r="93" spans="1:14">
+      <c r="A93" s="12">
+        <v>91</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G93" s="13">
+        <v>46386</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="L93" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
     </row>
     <row r="129" spans="1:14">
-      <c r="A129" s="65"/>
+      <c r="A129" s="58"/>
       <c r="B129"/>
-      <c r="C129" s="65"/>
+      <c r="C129" s="58"/>
       <c r="D129"/>
       <c r="E129"/>
       <c r="F129"/>
@@ -5669,9 +5697,9 @@
       <c r="N129"/>
     </row>
     <row r="130" spans="1:14">
-      <c r="A130" s="65"/>
+      <c r="A130" s="58"/>
       <c r="B130"/>
-      <c r="C130" s="65"/>
+      <c r="C130" s="58"/>
       <c r="D130"/>
       <c r="E130"/>
       <c r="F130"/>
@@ -5685,9 +5713,9 @@
       <c r="N130"/>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="65"/>
+      <c r="A131" s="58"/>
       <c r="B131"/>
-      <c r="C131" s="65"/>
+      <c r="C131" s="58"/>
       <c r="D131"/>
       <c r="E131"/>
       <c r="F131"/>
@@ -5701,9 +5729,9 @@
       <c r="N131"/>
     </row>
     <row r="132" spans="1:14">
-      <c r="A132" s="65"/>
+      <c r="A132" s="58"/>
       <c r="B132"/>
-      <c r="C132" s="65"/>
+      <c r="C132" s="58"/>
       <c r="D132"/>
       <c r="E132"/>
       <c r="F132"/>
@@ -5717,9 +5745,9 @@
       <c r="N132"/>
     </row>
     <row r="133" spans="1:14">
-      <c r="A133" s="65"/>
+      <c r="A133" s="58"/>
       <c r="B133"/>
-      <c r="C133" s="65"/>
+      <c r="C133" s="58"/>
       <c r="D133"/>
       <c r="E133"/>
       <c r="F133"/>
@@ -5733,9 +5761,9 @@
       <c r="N133"/>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="65"/>
+      <c r="A134" s="58"/>
       <c r="B134"/>
-      <c r="C134" s="65"/>
+      <c r="C134" s="58"/>
       <c r="D134"/>
       <c r="E134"/>
       <c r="F134"/>
@@ -5749,9 +5777,9 @@
       <c r="N134"/>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="65"/>
+      <c r="A135" s="58"/>
       <c r="B135"/>
-      <c r="C135" s="65"/>
+      <c r="C135" s="58"/>
       <c r="D135"/>
       <c r="E135"/>
       <c r="F135"/>
@@ -5765,9 +5793,9 @@
       <c r="N135"/>
     </row>
     <row r="136" spans="1:14">
-      <c r="A136" s="65"/>
+      <c r="A136" s="58"/>
       <c r="B136"/>
-      <c r="C136" s="65"/>
+      <c r="C136" s="58"/>
       <c r="D136"/>
       <c r="E136"/>
       <c r="F136"/>
@@ -5781,9 +5809,9 @@
       <c r="N136"/>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="65"/>
+      <c r="A137" s="58"/>
       <c r="B137"/>
-      <c r="C137" s="65"/>
+      <c r="C137" s="58"/>
       <c r="D137"/>
       <c r="E137"/>
       <c r="F137"/>
@@ -5797,9 +5825,9 @@
       <c r="N137"/>
     </row>
     <row r="138" spans="1:14">
-      <c r="A138" s="65"/>
+      <c r="A138" s="58"/>
       <c r="B138"/>
-      <c r="C138" s="65"/>
+      <c r="C138" s="58"/>
       <c r="D138"/>
       <c r="E138"/>
       <c r="F138"/>
@@ -5813,9 +5841,9 @@
       <c r="N138"/>
     </row>
     <row r="139" spans="1:14">
-      <c r="A139" s="65"/>
+      <c r="A139" s="58"/>
       <c r="B139"/>
-      <c r="C139" s="65"/>
+      <c r="C139" s="58"/>
       <c r="D139"/>
       <c r="E139"/>
       <c r="F139"/>
@@ -5829,9 +5857,9 @@
       <c r="N139"/>
     </row>
     <row r="140" spans="1:14">
-      <c r="A140" s="65"/>
+      <c r="A140" s="58"/>
       <c r="B140"/>
-      <c r="C140" s="65"/>
+      <c r="C140" s="58"/>
       <c r="D140"/>
       <c r="E140"/>
       <c r="F140"/>
@@ -5845,9 +5873,9 @@
       <c r="N140"/>
     </row>
     <row r="141" spans="1:14">
-      <c r="A141" s="65"/>
+      <c r="A141" s="58"/>
       <c r="B141"/>
-      <c r="C141" s="65"/>
+      <c r="C141" s="58"/>
       <c r="D141"/>
       <c r="E141"/>
       <c r="F141"/>
@@ -5861,9 +5889,9 @@
       <c r="N141"/>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="65"/>
+      <c r="A142" s="58"/>
       <c r="B142"/>
-      <c r="C142" s="65"/>
+      <c r="C142" s="58"/>
       <c r="D142"/>
       <c r="E142"/>
       <c r="F142"/>
@@ -5877,9 +5905,9 @@
       <c r="N142"/>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="65"/>
+      <c r="A143" s="58"/>
       <c r="B143"/>
-      <c r="C143" s="65"/>
+      <c r="C143" s="58"/>
       <c r="D143"/>
       <c r="E143"/>
       <c r="F143"/>
@@ -5893,9 +5921,9 @@
       <c r="N143"/>
     </row>
     <row r="144" spans="1:14">
-      <c r="A144" s="65"/>
+      <c r="A144" s="58"/>
       <c r="B144"/>
-      <c r="C144" s="65"/>
+      <c r="C144" s="58"/>
       <c r="D144"/>
       <c r="E144"/>
       <c r="F144"/>
@@ -5909,9 +5937,9 @@
       <c r="N144"/>
     </row>
     <row r="145" spans="1:14">
-      <c r="A145" s="65"/>
+      <c r="A145" s="58"/>
       <c r="B145"/>
-      <c r="C145" s="65"/>
+      <c r="C145" s="58"/>
       <c r="D145"/>
       <c r="E145"/>
       <c r="F145"/>
@@ -5925,9 +5953,9 @@
       <c r="N145"/>
     </row>
     <row r="146" spans="1:14">
-      <c r="A146" s="65"/>
+      <c r="A146" s="58"/>
       <c r="B146"/>
-      <c r="C146" s="65"/>
+      <c r="C146" s="58"/>
       <c r="D146"/>
       <c r="E146"/>
       <c r="F146"/>
@@ -5941,9 +5969,9 @@
       <c r="N146"/>
     </row>
     <row r="147" spans="1:14">
-      <c r="A147" s="65"/>
+      <c r="A147" s="58"/>
       <c r="B147"/>
-      <c r="C147" s="65"/>
+      <c r="C147" s="58"/>
       <c r="D147"/>
       <c r="E147"/>
       <c r="F147"/>
@@ -5957,9 +5985,9 @@
       <c r="N147"/>
     </row>
     <row r="148" spans="1:14">
-      <c r="A148" s="65"/>
+      <c r="A148" s="58"/>
       <c r="B148"/>
-      <c r="C148" s="65"/>
+      <c r="C148" s="58"/>
       <c r="D148"/>
       <c r="E148"/>
       <c r="F148"/>
@@ -5973,9 +6001,9 @@
       <c r="N148"/>
     </row>
     <row r="149" spans="1:14">
-      <c r="A149" s="65"/>
+      <c r="A149" s="58"/>
       <c r="B149"/>
-      <c r="C149" s="65"/>
+      <c r="C149" s="58"/>
       <c r="D149"/>
       <c r="E149"/>
       <c r="F149"/>
@@ -5989,9 +6017,9 @@
       <c r="N149"/>
     </row>
     <row r="150" spans="1:14">
-      <c r="A150" s="65"/>
+      <c r="A150" s="58"/>
       <c r="B150"/>
-      <c r="C150" s="65"/>
+      <c r="C150" s="58"/>
       <c r="D150"/>
       <c r="E150"/>
       <c r="F150"/>
@@ -6005,9 +6033,9 @@
       <c r="N150"/>
     </row>
     <row r="151" spans="1:14">
-      <c r="A151" s="65"/>
+      <c r="A151" s="58"/>
       <c r="B151"/>
-      <c r="C151" s="65"/>
+      <c r="C151" s="58"/>
       <c r="D151"/>
       <c r="E151"/>
       <c r="F151"/>
@@ -6021,9 +6049,9 @@
       <c r="N151"/>
     </row>
     <row r="152" spans="1:14">
-      <c r="A152" s="65"/>
+      <c r="A152" s="58"/>
       <c r="B152"/>
-      <c r="C152" s="65"/>
+      <c r="C152" s="58"/>
       <c r="D152"/>
       <c r="E152"/>
       <c r="F152"/>
@@ -6037,9 +6065,9 @@
       <c r="N152"/>
     </row>
     <row r="153" spans="1:14">
-      <c r="A153" s="65"/>
+      <c r="A153" s="58"/>
       <c r="B153"/>
-      <c r="C153" s="65"/>
+      <c r="C153" s="58"/>
       <c r="D153"/>
       <c r="E153"/>
       <c r="F153"/>
@@ -6053,9 +6081,9 @@
       <c r="N153"/>
     </row>
     <row r="154" spans="1:14">
-      <c r="A154" s="65"/>
+      <c r="A154" s="58"/>
       <c r="B154"/>
-      <c r="C154" s="65"/>
+      <c r="C154" s="58"/>
       <c r="D154"/>
       <c r="E154"/>
       <c r="F154"/>
@@ -6069,9 +6097,9 @@
       <c r="N154"/>
     </row>
     <row r="155" spans="1:14">
-      <c r="A155" s="65"/>
+      <c r="A155" s="58"/>
       <c r="B155"/>
-      <c r="C155" s="65"/>
+      <c r="C155" s="58"/>
       <c r="D155"/>
       <c r="E155"/>
       <c r="F155"/>
@@ -6085,9 +6113,9 @@
       <c r="N155"/>
     </row>
     <row r="156" spans="1:14">
-      <c r="A156" s="65"/>
+      <c r="A156" s="58"/>
       <c r="B156"/>
-      <c r="C156" s="65"/>
+      <c r="C156" s="58"/>
       <c r="D156"/>
       <c r="E156"/>
       <c r="F156"/>
@@ -6101,9 +6129,9 @@
       <c r="N156"/>
     </row>
     <row r="157" spans="1:14">
-      <c r="A157" s="65"/>
+      <c r="A157" s="58"/>
       <c r="B157"/>
-      <c r="C157" s="65"/>
+      <c r="C157" s="58"/>
       <c r="D157"/>
       <c r="E157"/>
       <c r="F157"/>
@@ -6117,9 +6145,9 @@
       <c r="N157"/>
     </row>
     <row r="158" spans="1:14">
-      <c r="A158" s="65"/>
+      <c r="A158" s="58"/>
       <c r="B158"/>
-      <c r="C158" s="65"/>
+      <c r="C158" s="58"/>
       <c r="D158"/>
       <c r="E158"/>
       <c r="F158"/>
@@ -6132,71 +6160,63 @@
       <c r="M158"/>
       <c r="N158"/>
     </row>
+    <row r="159" spans="1:14">
+      <c r="A159" s="58"/>
+      <c r="B159"/>
+      <c r="C159" s="58"/>
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159"/>
+      <c r="L159"/>
+      <c r="M159"/>
+      <c r="N159"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="59">
+  <mergeCells count="35">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A89:A92"/>
     <mergeCell ref="B3:B10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="B34:B58"/>
-    <mergeCell ref="B59:B69"/>
-    <mergeCell ref="B70:B85"/>
-    <mergeCell ref="B86:B92"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="B17:B28"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B35:B59"/>
+    <mergeCell ref="B60:B70"/>
+    <mergeCell ref="B71:B86"/>
+    <mergeCell ref="B87:B93"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="C49:C53"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="C73:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C85"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="C89:C92"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C62:C67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C90:C93"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66 H1:H58 H59:H60 H61:H62 H63:H65 H67:H68 H69:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13 H1:H12 H14:H16 H17:H1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
